--- a/output/full_scan/batch_seq0_2026-06-11.xlsx
+++ b/output/full_scan/batch_seq0_2026-06-11.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8487</v>
+        <v>8071</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1041.406193362741</v>
+        <v>1256.3080190728</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>83.09999999999999</v>
+        <v>24.95</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.60544035017465</v>
+        <v>67.535255767264</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20.4398608915409</v>
+        <v>38.39021953978931</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.140619336274057</v>
+        <v>2.630801907280008</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1801640177929914</v>
+        <v>0.1324481522558067</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8071</v>
+        <v>8487</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>981.3080190728</v>
+        <v>1242.112991762608</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>24.95</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>67.53525580407681</v>
+        <v>61.60544035017465</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>38.39021955532587</v>
+        <v>20.43986087591552</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.630801907280008</v>
+        <v>4.211299176260765</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1324481522844236</v>
+        <v>0.1801640177929914</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>9914</v>
+        <v>8182</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>美利達</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>890.1719036866778</v>
+        <v>1167.549899219265</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>73.7</v>
+        <v>54.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>70.00970647406535</v>
+        <v>70.15734627368406</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29.02241532157754</v>
+        <v>25.36878356483137</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.017190368667777</v>
+        <v>2.754989921926526</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2770456022276328</v>
+        <v>0.7207417287207312</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8182</v>
+        <v>9914</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>美利達</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>802.5498992192653</v>
+        <v>1160.501887212856</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>54.5</v>
+        <v>73.7</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>70.15734628561243</v>
+        <v>70.0097063433422</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25.3687835456296</v>
+        <v>29.02241535635959</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.754989921926526</v>
+        <v>2.050188721285576</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,11 +729,11 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.7207417287111899</v>
+        <v>0.2770456020368479</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>789.7635239049213</v>
+        <v>1079.763523904921</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>43.5</v>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>64.18633444241233</v>
+        <v>64.18633442431299</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>43.95938651985548</v>
+        <v>43.95938661620573</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.476352390492132</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0357399261034023</v>
+        <v>0.0357399260747817</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8150</v>
+        <v>8926</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>788.0699232303353</v>
+        <v>1055.905082118157</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>97.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>55.37613761347333</v>
+        <v>70.87472929635408</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.54535339993686</v>
+        <v>53.51156880014967</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.30699232303353</v>
+        <v>1.090508211815713</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-1.028542414624487</v>
+        <v>0.2720355565146981</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8926</v>
+        <v>8150</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>780.8066030881822</v>
+        <v>1043.181090089737</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>75.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>70.87472930770662</v>
+        <v>55.37613761009175</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>53.51156879028479</v>
+        <v>26.54535339974116</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.080660308818222</v>
+        <v>1.318109008973728</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2720355565242354</v>
+        <v>-1.028542414643576</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8473</v>
+        <v>9910</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>719.8541978871299</v>
+        <v>1039.024410177698</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>65.93225384471347</v>
+        <v>78.10760560808242</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>47.89131879291792</v>
+        <v>30.56005529239124</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9854197887129864</v>
+        <v>2.402441017769748</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2133050711867676</v>
+        <v>2.861671141063749</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9910</v>
+        <v>8163</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>718.8695392025776</v>
+        <v>938.5145024320238</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>78.10760575172132</v>
+        <v>72.69879221248604</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30.56005530132049</v>
+        <v>51.34053586239327</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.386953920257761</v>
+        <v>0.8514502432023846</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.861671141254535</v>
+        <v>0.2096252359065915</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8070</v>
+        <v>8473</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>705.3629721990209</v>
+        <v>924.9385385766568</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>58.8</v>
+        <v>52</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.35495657477498</v>
+        <v>65.93225381960104</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>33.347237627361</v>
+        <v>47.8913187936472</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.03629721990209</v>
+        <v>0.9938538576656728</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.5882828778441009</v>
+        <v>0.2133050711390591</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8076</v>
+        <v>8341</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>704.5240204977407</v>
+        <v>905.3291198334308</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>26.9</v>
+        <v>81</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.89687644758284</v>
+        <v>70.94170750979856</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>26.54818077649633</v>
+        <v>24.80413742280008</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9524020497740668</v>
+        <v>1.532911983343087</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2088456668306064</v>
+        <v>0.5517490289591855</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8163</v>
+        <v>8210</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>698.4376582018398</v>
+        <v>893.7562269071148</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>43</v>
+        <v>1440</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>72.69879224663717</v>
+        <v>56.55971319284448</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>51.34053588274875</v>
+        <v>28.3498308596718</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.8437658201839804</v>
+        <v>0.8756226907114759</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.2096252359065915</v>
+        <v>-6.164557563700761</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>9105</v>
+        <v>8050</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>698.16785798884</v>
+        <v>879.4871873730307</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9.24</v>
+        <v>58.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.18378171660417</v>
+        <v>61.35825429270237</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>52.14223401666814</v>
+        <v>52.15849317192284</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.816785798883999</v>
+        <v>0.4487187373030721</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.0450186444381355</v>
+        <v>-0.3966583179757581</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>9136</v>
+        <v>8109</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>696.5858627093354</v>
+        <v>873.268995348078</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>15.8</v>
+        <v>118.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>68.72074287661472</v>
+        <v>47.20337727721269</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>53.9015383608694</v>
+        <v>30.25224327367852</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6585862709335391</v>
+        <v>0.3268995348078021</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.3332728839271537</v>
+        <v>-0.8211955759854432</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8112</v>
+        <v>8476</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>694.8745477071151</v>
+        <v>865.5141181856529</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>95.5</v>
+        <v>19.15</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>60.59281300828301</v>
+        <v>74.93989271247065</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22.69346697503937</v>
+        <v>33.76048652076699</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.487454770711509</v>
+        <v>2.051411818565299</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4334228785804865</v>
+        <v>0.5174150381227081</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8476</v>
+        <v>8112</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>665.399589404009</v>
+        <v>849.9852936292797</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>19.15</v>
+        <v>95.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>74.93989285385854</v>
+        <v>60.59281298761316</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>33.76048649897885</v>
+        <v>22.69346697593646</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.039958940400902</v>
+        <v>1.498529362927969</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.5174150381036281</v>
+        <v>0.4334228785804865</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8096</v>
+        <v>8289</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>656.3601738674379</v>
+        <v>840.1588565274097</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>121</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.69418819700296</v>
+        <v>63.74153812227127</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>43.54382617783421</v>
+        <v>37.61050160022126</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6360173867437932</v>
+        <v>1.015885652740973</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-1.570282012846285</v>
+        <v>-0.5989772011406949</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8261</v>
+        <v>9136</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>644.864695067791</v>
+        <v>836.5955704050542</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>158</v>
+        <v>15.8</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>51.16435099967672</v>
+        <v>68.72074287630645</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>37.3552732656313</v>
+        <v>53.90153840044926</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4864695067790948</v>
+        <v>0.6595570405054214</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-3.800717240250768</v>
+        <v>0.3332728839653116</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8097</v>
+        <v>8070</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>641.8394439365798</v>
+        <v>815.4116223682175</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>59.1</v>
+        <v>58.8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60.669158990138</v>
+        <v>63.35495654529389</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>33.52869621627335</v>
+        <v>33.34723764303886</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.183944393657971</v>
+        <v>1.041162236821752</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.0685412120447481</v>
+        <v>0.5882828778536435</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8289</v>
+        <v>8097</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>640.1588565274097</v>
+        <v>811.8394439365798</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>59.1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>63.74153812227127</v>
+        <v>60.66915889785358</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>37.61050159410378</v>
+        <v>33.52869629950342</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.015885652740973</v>
+        <v>1.183944393657971</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.598977201083458</v>
+        <v>-0.0685412117776396</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8109</v>
+        <v>8488</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>638.268995348078</v>
+        <v>803.5450891610396</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>118.5</v>
+        <v>10.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>47.20337730474297</v>
+        <v>54.23797214502852</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>30.25224331982442</v>
+        <v>8.774438410627305</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.3268995348078021</v>
+        <v>1.354508916103966</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.8211955759663618</v>
+        <v>0.0281584424446463</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8488</v>
+        <v>9105</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>633.4863065822809</v>
+        <v>768.1975669460173</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10.5</v>
+        <v>9.24</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>54.23797212331667</v>
+        <v>56.18378169456227</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>8.774438426341824</v>
+        <v>52.14223406818264</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.348630658228092</v>
+        <v>0.8197566946017371</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0281584424923454</v>
+        <v>-0.0450186444305029</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8088</v>
+        <v>8472</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>622.76296141877</v>
+        <v>762.2042771599657</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>57.7</v>
+        <v>89</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>48.7806716710229</v>
+        <v>65.69881439784979</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.82514307260896</v>
+        <v>34.06548323231738</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2762961418770039</v>
+        <v>0.7204277159965783</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.612132033581088</v>
+        <v>1.179398924896735</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8472</v>
+        <v>8996</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>622.2042771599657</v>
+        <v>761.2662703574892</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>89</v>
+        <v>1140</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>65.69881520089068</v>
+        <v>50.88413508867564</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>34.06548321771239</v>
+        <v>14.33928783347659</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7204277159965783</v>
+        <v>1.12662703574893</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.179398924639155</v>
+        <v>8.531610049654329</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8131</v>
+        <v>8105</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>620.9075672151645</v>
+        <v>760.0857499646806</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>68.7</v>
+        <v>20.45</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>51.57531800116972</v>
+        <v>64.40435298344038</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>14.08924760593054</v>
+        <v>41.32528770575691</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.590756721516446</v>
+        <v>1.008574996468065</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.373997141175955</v>
+        <v>0.1550420507016883</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8215</v>
+        <v>8081</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>619.8332680249637</v>
+        <v>751.8630265576468</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>28.55</v>
+        <v>273</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.51200566077405</v>
+        <v>51.57873039154631</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25.2347927500091</v>
+        <v>28.23539058834439</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4833268024963623</v>
+        <v>0.68630265576468</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.3065644367945437</v>
+        <v>-3.30095338202545</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8050</v>
+        <v>9906</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>619.4871873730307</v>
+        <v>750</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>58.5</v>
+        <v>43.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>61.35825436529345</v>
+        <v>66.22000314680145</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>52.1584931093424</v>
+        <v>33.46793218414477</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4487187373030721</v>
+        <v>5.484019733936186</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.3966583179375997</v>
+        <v>1.256254050238966</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8081</v>
+        <v>8462</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>611.7121392068012</v>
+        <v>735.0710951620958</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>273</v>
+        <v>144</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.57873043666646</v>
+        <v>57.97066839511152</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.23539058108699</v>
+        <v>16.01393445489003</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.671213920680117</v>
+        <v>1.507109516209581</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-3.300953381930062</v>
+        <v>0.5763101266909536</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8210</v>
+        <v>8215</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>608.3761618680304</v>
+        <v>734.8785552358619</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1440</v>
+        <v>28.55</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.55971318731464</v>
+        <v>49.51200562704408</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>28.34983085429136</v>
+        <v>25.23479276693679</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8376161868030385</v>
+        <v>0.4878555235861858</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-6.164557563605264</v>
+        <v>-0.3065644367945437</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8105</v>
+        <v>8481</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>605.0666957597673</v>
+        <v>722.6012354493619</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>20.45</v>
+        <v>41.4</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>64.40435298597691</v>
+        <v>57.72213232824539</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>41.32528769131969</v>
+        <v>21.52805272502058</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.006669575976734</v>
+        <v>0.7601235449361889</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1550420506921486</v>
+        <v>0.07331083342321271</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8390</v>
+        <v>8087</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>586.1516358576127</v>
+        <v>721.5690848588632</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>110.5</v>
+        <v>34.1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45.14511869536066</v>
+        <v>48.06538621423042</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>39.02003992664465</v>
+        <v>26.97393058847069</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.115163585761281</v>
+        <v>2.656908485886319</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-1.638625568366249</v>
+        <v>0.2994016950318526</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8087</v>
+        <v>9908</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>581.5690848588632</v>
+        <v>707.4595805867025</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>34.1</v>
+        <v>29.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>48.06538634844338</v>
+        <v>55.82961663245307</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>26.97393049695189</v>
+        <v>13.04186432357451</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.656908485886319</v>
+        <v>0.7459580586702445</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.2994016950509367</v>
+        <v>0.0514209468997738</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8341</v>
+        <v>8076</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>574.9083485975671</v>
+        <v>704.5240204977407</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>81</v>
+        <v>26.9</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>70.94170765974405</v>
+        <v>60.89687641586848</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24.80413738219743</v>
+        <v>26.54818085224009</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.490834859756699</v>
+        <v>0.9524020497740668</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.5517490289401081</v>
+        <v>0.2088456667829077</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8104</v>
+        <v>8499</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>567.7432991027811</v>
+        <v>700.1762521020045</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>38.6</v>
+        <v>287</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>50.88192922772264</v>
+        <v>48.82298210743269</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>31.8330955101904</v>
+        <v>16.77744150747701</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.2743299102781017</v>
+        <v>0.5176252102004419</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.1114896436934875</v>
+        <v>-4.346957720265415</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8069</v>
+        <v>8088</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>561.3978489477694</v>
+        <v>697.76296141877</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>190.5</v>
+        <v>57.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>43.01141836451327</v>
+        <v>48.78067167739188</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>33.27264272253998</v>
+        <v>23.82514302530871</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.139784894776937</v>
+        <v>0.2762961418770039</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-7.038835267674298</v>
+        <v>-0.6121320331136424</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8499</v>
+        <v>8411</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>559.9397884123964</v>
+        <v>687.4156253463855</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>287</v>
+        <v>12.2</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>48.82298210974152</v>
+        <v>52.58834632342011</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16.77744150958337</v>
+        <v>28.81223851142657</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4939788412396336</v>
+        <v>2.241562534638546</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-4.346957720265415</v>
+        <v>0.0262332068598468</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8162</v>
+        <v>8093</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>558.7244100312545</v>
+        <v>678.1666120445826</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>18.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.53354367949251</v>
+        <v>51.85597616610477</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>43.75068446661342</v>
+        <v>9.818891745204768</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3724410031254488</v>
+        <v>0.3166612044582637</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.556264847326384</v>
+        <v>-0.247690971641558</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>9906</v>
+        <v>9905</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>550</v>
+        <v>669.6756127066625</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>43.7</v>
+        <v>20.7</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>66.22000337878436</v>
+        <v>46.03190029681758</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>33.46793218039296</v>
+        <v>21.64372589449277</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5.431221103473493</v>
+        <v>0.9675612706662484</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,11 +2531,11 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.2562540497429</v>
+        <v>0.0001154269639029</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>544.9782612618154</v>
+        <v>660.018410146716</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>5.75</v>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>59.78852991153762</v>
+        <v>59.78852980090696</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>42.60916377921865</v>
+        <v>42.60916377921867</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9978261261815397</v>
+        <v>1.001841014671598</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,11 +2584,11 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0522351804369994</v>
+        <v>0.0522351804465397</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>544.8244090860767</v>
+        <v>659.8244090860768</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>26.15</v>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45.27959584027471</v>
+        <v>45.27959573287769</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>23.55936358072848</v>
+        <v>23.55936368049264</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.4824409086076757</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.1303408824783196</v>
+        <v>-0.1303408824687828</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>9908</v>
+        <v>8096</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>527.341734125092</v>
+        <v>656.3601738674379</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>29.5</v>
+        <v>121</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.82961668857191</v>
+        <v>54.69418815102309</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.04186438567115</v>
+        <v>43.54382615212209</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.7341734125091911</v>
+        <v>0.6360173867437932</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.051420946909319</v>
+        <v>-1.570282012636422</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8227</v>
+        <v>8261</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>522.8552508301973</v>
+        <v>644.9585491441941</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>173.5</v>
+        <v>158</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>39.93364591353984</v>
+        <v>51.1643509714925</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>29.35894216757045</v>
+        <v>37.35527316884396</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.285525083019726</v>
+        <v>0.4958549144194049</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-7.515094089391996</v>
+        <v>-3.800717240002744</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>9110</v>
+        <v>8422</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>522.782916168743</v>
+        <v>644.3092936922618</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>3.44</v>
+        <v>29.25</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>57.17419685735714</v>
+        <v>57.3133272528878</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.06491201638744</v>
+        <v>17.99241915527596</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.278291616874294</v>
+        <v>1.930929369226182</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0621487426936843</v>
+        <v>0.3759398136360944</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8411</v>
+        <v>9911</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>517.2650455851596</v>
+        <v>641.9906155336994</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>12.2</v>
+        <v>84.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.58834650512396</v>
+        <v>59.59611824995</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>28.81223719593505</v>
+        <v>19.82591100779494</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.226504558515953</v>
+        <v>0.6990615533699382</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0262332067549104</v>
+        <v>0.3783537414678815</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8064</v>
+        <v>8464</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>513.1306346131291</v>
+        <v>633.3907110930539</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>133</v>
+        <v>337</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,49 +2884,49 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.92970179490242</v>
+        <v>55.52778469567189</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>44.6179919379591</v>
+        <v>23.08536832161126</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.8130634613129073</v>
+        <v>0.3390711093053923</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-3.565252639905735</v>
+        <v>3.742195436021823</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8481</v>
+        <v>8131</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>512.5591353144898</v>
+        <v>620.9676770148002</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>41.4</v>
+        <v>68.7</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>57.72213253880412</v>
+        <v>51.5753179904915</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>21.52805272142031</v>
+        <v>14.08924759736737</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7559135314489868</v>
+        <v>0.5967677014800239</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.07331083344228689</v>
+        <v>-0.3739971411187088</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8455</v>
+        <v>8940</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>511.1029005833839</v>
+        <v>613.0197565915398</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>29.6</v>
+        <v>16.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>41.52466906724069</v>
+        <v>45.59504627758427</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>30.72495283323267</v>
+        <v>12.97412833774914</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.1102900583383922</v>
+        <v>2.301975659153984</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-2.036519141142319</v>
+        <v>0.0227560961904687</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8091</v>
+        <v>8227</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>509.5428610774798</v>
+        <v>612.8552508301973</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>237</v>
+        <v>173.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>50.62789275709521</v>
+        <v>39.93364589982456</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>36.23193220185314</v>
+        <v>29.3589421745658</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4542861077479761</v>
+        <v>1.285525083019726</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-5.680017124995462</v>
+        <v>-7.515094089773574</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8462</v>
+        <v>8390</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>504.7303190601621</v>
+        <v>586.1516358576127</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>144</v>
+        <v>110.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>57.97066843805355</v>
+        <v>45.14511876850828</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>16.01393442855257</v>
+        <v>39.02003995497341</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.473031906016211</v>
+        <v>1.115163585761281</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.5763101271679308</v>
+        <v>-1.638625568328073</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8271</v>
+        <v>9904</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>504.4388462345357</v>
+        <v>579.2523122231078</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>197</v>
+        <v>26.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>37.60905512006208</v>
+        <v>51.51382625379318</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>26.47488707851508</v>
+        <v>22.80815316549245</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9438846234535718</v>
+        <v>0.9252312223107818</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-6.525004690310524</v>
+        <v>0.1374641743062314</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8374</v>
+        <v>8104</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>501.8999187464285</v>
+        <v>567.7741891964392</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>38.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>43.14693373211534</v>
+        <v>50.8819292002748</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>26.63633173155338</v>
+        <v>31.83309551739212</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.1899918746428484</v>
+        <v>0.2774189196439273</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-2.768523078318408</v>
+        <v>-0.1114896437125634</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>9905</v>
+        <v>8114</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>499.6173238815893</v>
+        <v>561.4139247195703</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>20.7</v>
+        <v>208</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46.03190025398078</v>
+        <v>43.22672032718729</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.64372585417016</v>
+        <v>33.50688507799566</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9617323881589268</v>
+        <v>1.141392471957041</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0001154269925223</v>
+        <v>-7.499581271362509</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8086</v>
+        <v>8069</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>490.3178996254685</v>
+        <v>561.3978489477694</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>145.5</v>
+        <v>190.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>43.5394009811366</v>
+        <v>43.01141836156859</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>23.04335490605558</v>
+        <v>33.2726426820125</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5317899625468416</v>
+        <v>1.139784894776937</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-2.89817008357164</v>
+        <v>-7.038835268246689</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8940</v>
+        <v>9912</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>488.7129039542617</v>
+        <v>557.0863999728678</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>16.7</v>
+        <v>12.6</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45.59504627758427</v>
+        <v>55.00942650442603</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.97412813814588</v>
+        <v>17.96322388531548</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.871290395426172</v>
+        <v>0.2086399972867715</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0227560961046097</v>
+        <v>0.0079375119421173</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8110</v>
+        <v>9907</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>480.5635008110465</v>
+        <v>545.3372592497149</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>53.6</v>
+        <v>16.75</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.75001500936872</v>
+        <v>53.86416146039223</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>17.047110195277</v>
+        <v>28.37532673574782</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5563500811046546</v>
+        <v>1.033725924971481</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.778954090861768</v>
+        <v>0.1347857114633077</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8102</v>
+        <v>8162</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>478.7636097272438</v>
+        <v>538.7724458226641</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>72</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.44833425567587</v>
+        <v>50.53354368902193</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.60708684502292</v>
+        <v>43.75068450262425</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3763609727243756</v>
+        <v>0.3772445822664059</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1622684469424222</v>
+        <v>-1.556264847450418</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8093</v>
+        <v>8466</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>478.1666120445826</v>
+        <v>530.8565277033949</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>18.7</v>
+        <v>16</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.85597619938668</v>
+        <v>51.85397934734307</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9.818891513490266</v>
+        <v>28.67400052600027</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3166612044582637</v>
+        <v>0.5856527703394901</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.2476909717069557</v>
+        <v>0.0901241720200745</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8299</v>
+        <v>9110</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>477.7415810151562</v>
+        <v>522.8009132042641</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2200</v>
+        <v>3.44</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>44.1168267835189</v>
+        <v>57.17419448241907</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.82460688688285</v>
+        <v>20.06491202204603</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7741581015156178</v>
+        <v>0.2800913204264184</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-72.20182940782348</v>
+        <v>0.0621487427108557</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8996</v>
+        <v>8429</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>476.0056430024589</v>
+        <v>515.6062783480331</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1140</v>
+        <v>6.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.88413509442031</v>
+        <v>55.28389835949401</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14.33928783767906</v>
+        <v>28.31286901231698</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.10056430024589</v>
+        <v>0.5606278348033077</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>8.53161005032219</v>
+        <v>0.0564722644034063</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8114</v>
+        <v>8064</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>451.2820232521798</v>
+        <v>513.1306346131291</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>43.22672036158563</v>
+        <v>48.92970179359921</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>33.50688504886696</v>
+        <v>44.61799197357824</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.128202325217985</v>
+        <v>0.8130634613129073</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-7.499581270980897</v>
+        <v>-3.5652526399439</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8477</v>
+        <v>8455</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>451.1184138280697</v>
+        <v>511.1029005833839</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>16.8</v>
+        <v>29.6</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45.92304271780306</v>
+        <v>41.5246690661686</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>36.77904425900142</v>
+        <v>30.7249528206162</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6118413828069692</v>
+        <v>0.1102900583383922</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.3200609919321349</v>
+        <v>-2.036519141199557</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8464</v>
+        <v>8091</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>443.350743066</v>
+        <v>509.5428610774798</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>337</v>
+        <v>237</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>55.52778478484207</v>
+        <v>50.62789275166971</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.08536835174585</v>
+        <v>36.23193227707518</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3350743066000018</v>
+        <v>0.4542861077479761</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>3.742195435926394</v>
+        <v>-5.680017124900076</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8101</v>
+        <v>8176</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>440.2483626639338</v>
+        <v>504.4824862357647</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>15.05</v>
+        <v>10.25</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>53.71904902414617</v>
+        <v>48.83162496726126</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.21340196559722</v>
+        <v>10.9166281042292</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.024836266393377</v>
+        <v>0.9482486235764724</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1539327751824937</v>
+        <v>0.027311506514396</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8249</v>
+        <v>8374</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>422.4989251549385</v>
+        <v>501.9357185962736</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>49.4</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>40.57191640242316</v>
+        <v>43.14693371494673</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.46473835432841</v>
+        <v>26.6363317322439</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.249892515493848</v>
+        <v>0.1935718596273585</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.710626586358918</v>
+        <v>-2.768523078585524</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>9904</v>
+        <v>8383</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>409.2182644471483</v>
+        <v>498.7824968807699</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>26.3</v>
+        <v>58.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>51.51382635071398</v>
+        <v>48.58081591816725</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.80815312839659</v>
+        <v>17.77425919597858</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9218264447148328</v>
+        <v>0.3782496880769859</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.1374641743253114</v>
+        <v>-0.3799290843793471</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8422</v>
+        <v>8086</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>404.2080422752434</v>
+        <v>490.3178996254685</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>29.25</v>
+        <v>145.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>57.31332753900672</v>
+        <v>43.53940096034653</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>17.99241915527596</v>
+        <v>23.04335488904938</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.920804227524344</v>
+        <v>0.5317899625468416</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.3759398136360944</v>
+        <v>-2.898170083552559</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8429</v>
+        <v>8271</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>400.4696015952143</v>
+        <v>489.6305315532047</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>6.6</v>
+        <v>197</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>55.28389847333851</v>
+        <v>37.60905510256569</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>28.31286900106939</v>
+        <v>26.47488703342462</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5469601595214277</v>
+        <v>0.9630531553204644</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0564722644072215</v>
+        <v>-6.525004689967113</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8466</v>
+        <v>8089</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>390.8275801155682</v>
+        <v>488.1106145002765</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>16</v>
+        <v>20.8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.85397939141929</v>
+        <v>49.92464206085538</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>28.67400053351575</v>
+        <v>26.20642379724885</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5827580115568198</v>
+        <v>1.311061450027647</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0901241720963932</v>
+        <v>0.1408368164613335</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>9912</v>
+        <v>8110</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>386.939459175748</v>
+        <v>480.5989318239475</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>12.6</v>
+        <v>53.6</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>55.00942631692251</v>
+        <v>48.75001499880484</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.9632238782736</v>
+        <v>17.0471101851357</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.1939459175748032</v>
+        <v>0.5598931823947487</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.007937511951656</v>
+        <v>-0.7789540908140731</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8383</v>
+        <v>8102</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>383.7824968807699</v>
+        <v>478.7636097272438</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>58.2</v>
+        <v>72</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>48.58081594950249</v>
+        <v>53.44833426385917</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.77425920686176</v>
+        <v>15.60708677855374</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3782496880769859</v>
+        <v>0.3763609727243756</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.3799290843316438</v>
+        <v>0.162268446789791</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>9911</v>
+        <v>8299</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>381.7120100232683</v>
+        <v>477.7415810151562</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>84.7</v>
+        <v>2200</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,49 +4262,49 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>59.59611837258392</v>
+        <v>44.11682677944991</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>19.82591104421689</v>
+        <v>19.82460691858367</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6712010023268301</v>
+        <v>0.7741581015156178</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.3783537414297163</v>
+        <v>-72.20182940744222</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>9907</v>
+        <v>8477</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>375.3117547454517</v>
+        <v>451.1184138280697</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>16.75</v>
+        <v>16.8</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.86416158726411</v>
+        <v>45.92304281516252</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>28.37532672956186</v>
+        <v>36.77904420477115</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.031175474545171</v>
+        <v>0.6118413828069692</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1347857114346891</v>
+        <v>-0.3200609919416746</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8176</v>
+        <v>8074</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>364.4824862357647</v>
+        <v>444.3769316016284</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>10.25</v>
+        <v>70</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>48.8316251700223</v>
+        <v>43.26639651791261</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10.91662802014425</v>
+        <v>12.14838461127762</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.9482486235764724</v>
+        <v>0.937693160162836</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0273115064762363</v>
+        <v>-0.8849290112896693</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8072</v>
+        <v>8478</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>359.4443112715174</v>
+        <v>441.406994892594</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>28.05</v>
+        <v>152</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.2540482465057</v>
+        <v>41.954692931114</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>25.80387351071849</v>
+        <v>20.59081925849513</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4444311271517454</v>
+        <v>2.64069948925939</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0189491395977522</v>
+        <v>0.9929210303990184</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8067</v>
+        <v>8101</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>347.8312385441215</v>
+        <v>441.365987997262</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>12.3</v>
+        <v>15.05</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.73893233217208</v>
+        <v>53.71905015625882</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7.834064701106447</v>
+        <v>20.21340196559722</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.2831238544121497</v>
+        <v>1.136598799726198</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,11 +4492,11 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0672948389740857</v>
+        <v>0.1539327751824937</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>341.5448121087234</v>
+        <v>436.5448121087234</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>347.5</v>
@@ -4527,49 +4527,49 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>34.7215461670135</v>
+        <v>34.72154613726325</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>24.57506131497471</v>
+        <v>24.57506133396245</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.6544812108723376</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M77" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-8.335489143791726</v>
+        <v>-8.335489143982484</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8074</v>
+        <v>8367</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>329.3769316016284</v>
+        <v>416.0012000909386</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>70</v>
+        <v>40.2</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>43.26639652707702</v>
+        <v>29.70484453345409</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>12.14838461127762</v>
+        <v>27.22649058364095</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.937693160162836</v>
+        <v>0.6001200090938568</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.8849290112610515</v>
+        <v>-0.0144598181143118</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8478</v>
+        <v>9802</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>325.8777353498654</v>
+        <v>414.0829311238396</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>41.95469300166531</v>
+        <v>52.45207815081458</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20.59081920974836</v>
+        <v>16.74297581566513</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.587773534986535</v>
+        <v>0.9082931123839612</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.992921030685233</v>
+        <v>0.5344255437226468</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>9802</v>
+        <v>8080</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>324.0132794348596</v>
+        <v>412.0906951061895</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>79</v>
+        <v>28.4</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>52.45207832710975</v>
+        <v>52.80489806404456</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.74297584993344</v>
+        <v>34.64960198595381</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9013279434859568</v>
+        <v>0.2090695106189521</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.5344255435700094</v>
+        <v>0.0917615702452797</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8089</v>
+        <v>8442</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>318.1106145002765</v>
+        <v>406.6086627263595</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>20.8</v>
+        <v>40</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>49.92464226046833</v>
+        <v>32.05609820377147</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>26.20642375631953</v>
+        <v>27.49185936143463</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.311061450027647</v>
+        <v>0.6608662726359432</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.1408368170146363</v>
+        <v>0.4533260686204805</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8367</v>
+        <v>8932</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>315.9643184647845</v>
+        <v>404.4961001853746</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>40.2</v>
+        <v>98.2</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>29.70484470049898</v>
+        <v>48.25402132877205</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>27.22649057927998</v>
+        <v>21.16529981103446</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5964318464784427</v>
+        <v>0.9496100185374624</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.014459818104768</v>
+        <v>-0.3892452413997147</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8234</v>
+        <v>8404</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>308.2107511657333</v>
+        <v>403.3536562460087</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>63.7</v>
+        <v>17.25</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>42.37208450559858</v>
+        <v>52.20221081362058</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>24.05868729040888</v>
+        <v>18.39077334497595</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3210751165733234</v>
+        <v>0.8353656246008671</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,11 +4863,11 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.092514313412476</v>
+        <v>0.1311444840412542</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>304.7933885916421</v>
+        <v>394.7933885916421</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>54.9</v>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>33.73225041213215</v>
+        <v>33.73225036975799</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.41532536216576</v>
+        <v>18.41532538529948</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.4793388591642106</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.193944216828092</v>
+        <v>-1.193944216751774</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8147</v>
+        <v>8482</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>303.0378881688223</v>
+        <v>390.8792784582809</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>144.5</v>
+        <v>47.75</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>36.18347659972738</v>
+        <v>51.16682747584113</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>21.56586412352071</v>
+        <v>6.661846067371984</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.8037888168822273</v>
+        <v>0.5879278458280843</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-4.17830216392073</v>
+        <v>-0.0012047794623617</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8111</v>
+        <v>8072</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>300.2754508216984</v>
+        <v>379.535112751683</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>55.5</v>
+        <v>28.05</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>32.39367940996802</v>
+        <v>47.2540479855681</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>21.68159206237514</v>
+        <v>25.80387351071849</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5275450821698436</v>
+        <v>0.4535112751682978</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.9301165351200036</v>
+        <v>0.0189491402846115</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8201</v>
+        <v>8463</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>284.5614847555566</v>
+        <v>379.4404525564032</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>12.95</v>
+        <v>21.95</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.2799302743076</v>
+        <v>49.3359445209536</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>25.18713077751708</v>
+        <v>12.54159642337446</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4561484755556603</v>
+        <v>0.4440452556403159</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0469828625362279</v>
+        <v>0.08879815526614231</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8183</v>
+        <v>8249</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>279.8302432439434</v>
+        <v>352.5405886143771</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>30.45</v>
+        <v>49.4</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>40.17904567019954</v>
+        <v>40.57191635976282</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.6047598106841</v>
+        <v>23.46473836706842</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.483024324394335</v>
+        <v>0.2540588614377093</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0340968354247811</v>
+        <v>-0.7106265864543125</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8482</v>
+        <v>8423</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>275.3745742329475</v>
+        <v>351.9349981664436</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>47.75</v>
+        <v>17.8</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>51.16682751828657</v>
+        <v>48.88247986359058</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>6.661846063985114</v>
+        <v>11.34281021455259</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5374574232947484</v>
+        <v>0.6934998166443569</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0012047799775067</v>
+        <v>0.0308373989427254</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8932</v>
+        <v>8067</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>264.4961001853746</v>
+        <v>347.8312385441215</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>98.2</v>
+        <v>12.3</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>48.25402136301032</v>
+        <v>49.73893231184921</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>21.16529978259477</v>
+        <v>7.834064672807808</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.9496100185374624</v>
+        <v>0.2831238544121497</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.38924524136702</v>
+        <v>-0.06729483898362471</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8404</v>
+        <v>8443</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>263.3041123768098</v>
+        <v>345.8981507901117</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>17.25</v>
+        <v>11.45</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>52.2022108589673</v>
+        <v>50.67609579201</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.39077330493761</v>
+        <v>61.29300086193425</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.8304112376809808</v>
+        <v>0.0898150790111738</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1311444840984939</v>
+        <v>0.036277006660769</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8171</v>
+        <v>8054</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>262.1927099560405</v>
+        <v>334.7514749877453</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>22.9</v>
+        <v>99.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>44.09082387844752</v>
+        <v>41.63123417969813</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.38015229834809</v>
+        <v>12.01657553003375</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7192709956040507</v>
+        <v>0.475147498774524</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0402711144153313</v>
+        <v>-0.607010922582202</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>9902</v>
+        <v>9930</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>260.3820075828829</v>
+        <v>312.7789941387706</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>13.55</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>39.75065901801862</v>
+        <v>48.13973044648706</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>13.74871359022631</v>
+        <v>15.8658142963633</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5382007582882917</v>
+        <v>1.27789941387706</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0099373175286563</v>
+        <v>0.0988945452863025</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8463</v>
+        <v>8234</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>259.4371656999024</v>
+        <v>308.2107511657333</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>21.95</v>
+        <v>63.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.33594473662975</v>
+        <v>42.37208429437246</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>12.54159636349202</v>
+        <v>24.05868731767437</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4437165699902382</v>
+        <v>0.3210751165733234</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0887981551802853</v>
+        <v>-1.09251431278285</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8103</v>
+        <v>8201</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>254.9135804859029</v>
+        <v>304.5733831535684</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>94.2</v>
+        <v>12.95</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37.40696210719479</v>
+        <v>46.27993022731752</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.58919626632842</v>
+        <v>25.18713081123542</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4913580485902863</v>
+        <v>0.4573383153568303</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.555043508623</v>
+        <v>-0.0469828625648461</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8438</v>
+        <v>8147</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>254.4252810384576</v>
+        <v>303.0378881688223</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>80</v>
+        <v>144.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>41.01324122079699</v>
+        <v>36.18347657416015</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.37602249519568</v>
+        <v>21.565864107425</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4425281038457639</v>
+        <v>0.8037888168822273</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.206493799252953</v>
+        <v>-4.178302163901664</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8084</v>
+        <v>8111</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>249.5489775829421</v>
+        <v>300.2754508216984</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>46.9</v>
+        <v>55.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>51.74212258861586</v>
+        <v>32.3936793418215</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>21.46995181582623</v>
+        <v>21.68159206237514</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4548977582942072</v>
+        <v>0.5275450821698436</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0621903882272814</v>
+        <v>-0.9301165350913898</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8080</v>
+        <v>8183</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>242.0906951061895</v>
+        <v>279.8302432439434</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>28.4</v>
+        <v>30.45</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>52.80489835421341</v>
+        <v>40.17904562056475</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>34.64960209243875</v>
+        <v>14.60475973812446</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.2090695106189521</v>
+        <v>0.483024324394335</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.09176157009264251</v>
+        <v>-0.0340968354247811</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8443</v>
+        <v>8171</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>225.5744642044173</v>
+        <v>262.1927099560405</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>11.45</v>
+        <v>22.9</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>50.67609576113132</v>
+        <v>44.09082376396044</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>61.29300086927238</v>
+        <v>17.38015229834809</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.0574464204417342</v>
+        <v>0.7192709956040507</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.036277006660769</v>
+        <v>-0.0402711143771763</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8068</v>
+        <v>8103</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>224.2089239477128</v>
+        <v>255.0123490988753</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>18.45</v>
+        <v>94.2</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>29.8196727034338</v>
+        <v>37.4069620932821</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20.12629307657737</v>
+        <v>17.58919627212726</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.9208923947712838</v>
+        <v>0.5012349098875259</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0883605185726293</v>
+        <v>-1.555043508623</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8442</v>
+        <v>8438</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>216.5671708404863</v>
+        <v>254.4815662980357</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>32.05609835720495</v>
+        <v>41.01324119867768</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>27.49185930402836</v>
+        <v>16.37602246112254</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6567170840486289</v>
+        <v>0.4481566298035725</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.4533260685823235</v>
+        <v>-1.206493799214792</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8423</v>
+        <v>8467</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>211.9349981664436</v>
+        <v>249.6259475441364</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>17.8</v>
+        <v>124.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>48.88247986359058</v>
+        <v>37.14264278311897</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>11.34281017787797</v>
+        <v>19.02391124342145</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6934998166443569</v>
+        <v>0.4625947544136347</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.030837398914107</v>
+        <v>0.5582848146214552</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8092</v>
+        <v>8084</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>208.6102445657608</v>
+        <v>249.5489775829421</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>14.7</v>
+        <v>46.9</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>35.02920065621026</v>
+        <v>51.74212264045482</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>24.74881276356254</v>
+        <v>21.46995198829388</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3610244565760793</v>
+        <v>0.4548977582942072</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.4242771735053132</v>
+        <v>0.0621903879315544</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8467</v>
+        <v>8085</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>204.4963725514441</v>
+        <v>238.6811892030062</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>124.5</v>
+        <v>12.7</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>37.14264288156042</v>
+        <v>47.99550273660451</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>19.02391123036218</v>
+        <v>31.07079430878629</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4496372551444122</v>
+        <v>0.368118920300622</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.5582848146214552</v>
+        <v>0.162499922918824</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>9955</v>
+        <v>8068</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>203.3780130946917</v>
+        <v>224.2089239477128</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>26.25</v>
+        <v>18.45</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>32.04416126987398</v>
+        <v>29.81967268838905</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.56322085386394</v>
+        <v>20.12629316742344</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.8378013094691661</v>
+        <v>0.9208923947712838</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1014532948029955</v>
+        <v>-0.0883605187157267</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8440</v>
+        <v>9902</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>203.1440272892754</v>
+        <v>210.4830377202997</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>22.35</v>
+        <v>13.55</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>47.03741177352138</v>
+        <v>39.75065895551148</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.26134506298018</v>
+        <v>13.74871362132954</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3144027289275362</v>
+        <v>0.548303772029969</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1040905380239424</v>
+        <v>-0.009937317519117901</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8054</v>
+        <v>8092</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>194.7514749877452</v>
+        <v>208.6102445657608</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>99.5</v>
+        <v>14.7</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>41.63123420452337</v>
+        <v>35.029200638275</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.01657559821317</v>
+        <v>24.74881277001916</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.475147498774524</v>
+        <v>0.3610244565760793</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.6070109222769227</v>
+        <v>-0.4242771734862341</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8213</v>
+        <v>8440</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>177.1619451252838</v>
+        <v>203.1440272892754</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>35.2</v>
+        <v>22.35</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>40.45944215998499</v>
+        <v>47.03741169279329</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.75835043735164</v>
+        <v>18.26134505379709</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.7161945125283745</v>
+        <v>0.3144027289275362</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.5092067234166151</v>
+        <v>-0.1040905380144044</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8085</v>
+        <v>8213</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>163.6811892030062</v>
+        <v>197.2137266113212</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>12.7</v>
+        <v>35.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.99550287076082</v>
+        <v>40.45944213312441</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>31.07079427800814</v>
+        <v>18.75835043964155</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.368118920300622</v>
+        <v>0.7213726611321157</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1624999228711247</v>
+        <v>-0.509206723407076</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8431</v>
+        <v>9955</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>149.5397437422587</v>
+        <v>183.7500458767737</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>47.6</v>
+        <v>26.25</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>27.27364276479136</v>
+        <v>32.04416170926804</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.85161760470757</v>
+        <v>22.56322076485597</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9539743742258736</v>
+        <v>0.8750045876773738</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.7606042000898694</v>
+        <v>-0.1014532949174703</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>9930</v>
+        <v>8410</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>142.614076971267</v>
+        <v>176.1656208861779</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>34.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>48.13973036764818</v>
+        <v>42.24647902333761</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>15.8658142947748</v>
+        <v>19.1108697259528</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.261407697126699</v>
+        <v>0.1165620886177849</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.09889454536262419</v>
+        <v>-0.0021494088307735</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8059</v>
+        <v>8431</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>140.5542263699315</v>
+        <v>149.5397437422587</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>17.9</v>
+        <v>47.6</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.10273357754301</v>
+        <v>27.27364276479136</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.39143121334958</v>
+        <v>15.85161764917896</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5554226369931486</v>
+        <v>0.9539743742258736</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1640465838840068</v>
+        <v>-0.7606042000135522</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8222</v>
+        <v>8059</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>138.8610891698417</v>
+        <v>140.5542263699315</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>33.75</v>
+        <v>17.9</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>38.5558856601814</v>
+        <v>39.10273351940785</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.9364056630829</v>
+        <v>19.3914312462568</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8861089169841676</v>
+        <v>0.5554226369931486</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.2353144658096431</v>
+        <v>-0.1640465839507842</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8410</v>
+        <v>8222</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>61.16562088617785</v>
+        <v>68.95238430688086</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>34.2</v>
+        <v>33.75</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.24647917864996</v>
+        <v>38.55588551606218</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19.11086973931797</v>
+        <v>16.9364056630829</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.1165620886177849</v>
+        <v>0.8952384306880855</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0021494088116977</v>
+        <v>-0.2353144657524041</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
